--- a/projections/te_2026_combined.xlsx
+++ b/projections/te_2026_combined.xlsx
@@ -1134,28 +1134,28 @@
         <v>107.66</v>
       </c>
       <c r="H12" t="n">
-        <v>54.3</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>162.26</v>
+        <v>148.68</v>
       </c>
       <c r="J12" t="n">
         <v>86.43000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>40.02</v>
+        <v>51.02</v>
       </c>
       <c r="L12" t="n">
-        <v>134.07</v>
+        <v>121.85</v>
       </c>
       <c r="M12" t="n">
         <v>65.2</v>
       </c>
       <c r="N12" t="n">
-        <v>25.75</v>
+        <v>35.39</v>
       </c>
       <c r="O12" t="n">
-        <v>105.88</v>
+        <v>95.02</v>
       </c>
       <c r="P12" t="n">
         <v>105.73</v>
@@ -7364,28 +7364,28 @@
         <v>107.66</v>
       </c>
       <c r="H12" t="n">
-        <v>54.3</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>162.26</v>
+        <v>148.68</v>
       </c>
       <c r="J12" t="n">
         <v>86.43000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>40.02</v>
+        <v>51.02</v>
       </c>
       <c r="L12" t="n">
-        <v>134.07</v>
+        <v>121.85</v>
       </c>
       <c r="M12" t="n">
         <v>65.2</v>
       </c>
       <c r="N12" t="n">
-        <v>25.75</v>
+        <v>35.39</v>
       </c>
       <c r="O12" t="n">
-        <v>105.88</v>
+        <v>95.02</v>
       </c>
       <c r="P12" t="n">
         <v>105.73</v>

--- a/projections/te_2026_combined.xlsx
+++ b/projections/te_2026_combined.xlsx
@@ -2585,58 +2585,58 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Will Mallory</t>
+          <t>Tyler Higbee</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>143.257</v>
+        <v>29.288</v>
       </c>
       <c r="E37" t="n">
-        <v>0.866</v>
+        <v>0.228</v>
       </c>
       <c r="F37" t="n">
-        <v>11.671</v>
+        <v>3.128</v>
       </c>
       <c r="G37" t="n">
-        <v>31.19</v>
+        <v>7.43</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>13.08</v>
       </c>
       <c r="J37" t="n">
-        <v>25.36</v>
+        <v>5.86</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>10.85</v>
       </c>
       <c r="M37" t="n">
-        <v>19.52</v>
+        <v>4.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="P37" t="n">
-        <v>6.24</v>
+        <v>33.18</v>
       </c>
       <c r="Q37" t="n">
-        <v>24.95</v>
+        <v>-25.75</v>
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
@@ -2644,58 +2644,58 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tyler Higbee</t>
+          <t>Will Mallory</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>29.288</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.228</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>3.128</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>7.43</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>13.08</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>10.85</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>8.630000000000001</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>33.18</v>
+        <v>6.24</v>
       </c>
       <c r="Q38" t="n">
-        <v>-25.75</v>
+        <v>-6.24</v>
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -3580,58 +3580,58 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Oronde Gadsden II</t>
+          <t>Will Kacmarek</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>112.065</v>
+        <v>98.136</v>
       </c>
       <c r="E54" t="n">
-        <v>0.738</v>
+        <v>0.845</v>
       </c>
       <c r="F54" t="n">
-        <v>9.135</v>
+        <v>9.493</v>
       </c>
       <c r="G54" t="n">
-        <v>24.77</v>
+        <v>24.38</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>8.49</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>43.34</v>
       </c>
       <c r="J54" t="n">
-        <v>20.2</v>
+        <v>19.63</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>36.07</v>
       </c>
       <c r="M54" t="n">
-        <v>15.64</v>
+        <v>14.88</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>28.79</v>
       </c>
       <c r="P54" t="n">
-        <v>63.28</v>
+        <v>19.54</v>
       </c>
       <c r="Q54" t="n">
-        <v>-38.51</v>
+        <v>4.84</v>
       </c>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
@@ -3639,58 +3639,58 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Will Kacmarek</t>
+          <t>Nate Boerkircher</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>98.136</v>
+        <v>96.67700000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>0.845</v>
+        <v>0.952</v>
       </c>
       <c r="F55" t="n">
-        <v>9.493</v>
+        <v>8.895</v>
       </c>
       <c r="G55" t="n">
-        <v>24.38</v>
+        <v>24.27</v>
       </c>
       <c r="H55" t="n">
-        <v>8.49</v>
+        <v>7.9</v>
       </c>
       <c r="I55" t="n">
-        <v>43.34</v>
+        <v>43.62</v>
       </c>
       <c r="J55" t="n">
-        <v>19.63</v>
+        <v>19.83</v>
       </c>
       <c r="K55" t="n">
-        <v>6.27</v>
+        <v>5.9</v>
       </c>
       <c r="L55" t="n">
-        <v>36.07</v>
+        <v>36.72</v>
       </c>
       <c r="M55" t="n">
-        <v>14.88</v>
+        <v>15.38</v>
       </c>
       <c r="N55" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="O55" t="n">
-        <v>28.79</v>
+        <v>29.82</v>
       </c>
       <c r="P55" t="n">
-        <v>19.54</v>
+        <v>28.41</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.84</v>
+        <v>-4.14</v>
       </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
@@ -3698,58 +3698,58 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Nate Boerkircher</t>
+          <t>Jonnu Smith</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>96.67700000000001</v>
+        <v>84.90900000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>0.952</v>
+        <v>0.978</v>
       </c>
       <c r="F56" t="n">
-        <v>8.895</v>
+        <v>9.456</v>
       </c>
       <c r="G56" t="n">
-        <v>24.27</v>
+        <v>23.82</v>
       </c>
       <c r="H56" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
       <c r="I56" t="n">
-        <v>43.62</v>
+        <v>42.21</v>
       </c>
       <c r="J56" t="n">
-        <v>19.83</v>
+        <v>19.09</v>
       </c>
       <c r="K56" t="n">
-        <v>5.9</v>
+        <v>5.58</v>
       </c>
       <c r="L56" t="n">
-        <v>36.72</v>
+        <v>35.08</v>
       </c>
       <c r="M56" t="n">
-        <v>15.38</v>
+        <v>14.36</v>
       </c>
       <c r="N56" t="n">
-        <v>3.91</v>
+        <v>3.25</v>
       </c>
       <c r="O56" t="n">
-        <v>29.82</v>
+        <v>27.95</v>
       </c>
       <c r="P56" t="n">
-        <v>28.41</v>
+        <v>20.88</v>
       </c>
       <c r="Q56" t="n">
-        <v>-4.14</v>
+        <v>2.94</v>
       </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -3757,58 +3757,58 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jonnu Smith</t>
+          <t>Brock Wright</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>84.90900000000001</v>
+        <v>76.95</v>
       </c>
       <c r="E57" t="n">
-        <v>0.978</v>
+        <v>0.928</v>
       </c>
       <c r="F57" t="n">
-        <v>9.456</v>
+        <v>9.519</v>
       </c>
       <c r="G57" t="n">
-        <v>23.82</v>
+        <v>22.78</v>
       </c>
       <c r="H57" t="n">
-        <v>7.91</v>
+        <v>6.39</v>
       </c>
       <c r="I57" t="n">
-        <v>42.21</v>
+        <v>42.08</v>
       </c>
       <c r="J57" t="n">
-        <v>19.09</v>
+        <v>18.02</v>
       </c>
       <c r="K57" t="n">
-        <v>5.58</v>
+        <v>4.16</v>
       </c>
       <c r="L57" t="n">
-        <v>35.08</v>
+        <v>34.79</v>
       </c>
       <c r="M57" t="n">
-        <v>14.36</v>
+        <v>13.26</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>1.93</v>
       </c>
       <c r="O57" t="n">
-        <v>27.95</v>
+        <v>27.5</v>
       </c>
       <c r="P57" t="n">
-        <v>20.88</v>
+        <v>22.65</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.94</v>
+        <v>0.13</v>
       </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
@@ -3816,58 +3816,58 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Brock Wright</t>
+          <t>Foster Moreau</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>76.95</v>
+        <v>80.744</v>
       </c>
       <c r="E58" t="n">
-        <v>0.928</v>
+        <v>0.97</v>
       </c>
       <c r="F58" t="n">
-        <v>9.519</v>
+        <v>8.539</v>
       </c>
       <c r="G58" t="n">
-        <v>22.78</v>
+        <v>22.43</v>
       </c>
       <c r="H58" t="n">
-        <v>6.39</v>
+        <v>6.8</v>
       </c>
       <c r="I58" t="n">
-        <v>42.08</v>
+        <v>40.46</v>
       </c>
       <c r="J58" t="n">
-        <v>18.02</v>
+        <v>18.16</v>
       </c>
       <c r="K58" t="n">
-        <v>4.16</v>
+        <v>4.82</v>
       </c>
       <c r="L58" t="n">
-        <v>34.79</v>
+        <v>33.9</v>
       </c>
       <c r="M58" t="n">
-        <v>13.26</v>
+        <v>13.89</v>
       </c>
       <c r="N58" t="n">
-        <v>1.93</v>
+        <v>2.84</v>
       </c>
       <c r="O58" t="n">
-        <v>27.5</v>
+        <v>27.35</v>
       </c>
       <c r="P58" t="n">
-        <v>22.65</v>
+        <v>30.06</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.13</v>
+        <v>-7.63</v>
       </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -3875,58 +3875,58 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Foster Moreau</t>
+          <t>Brevyn Spann-Ford</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>80.744</v>
+        <v>89.812</v>
       </c>
       <c r="E59" t="n">
-        <v>0.97</v>
+        <v>0.736</v>
       </c>
       <c r="F59" t="n">
-        <v>8.539</v>
+        <v>8.977</v>
       </c>
       <c r="G59" t="n">
-        <v>22.43</v>
+        <v>22.37</v>
       </c>
       <c r="H59" t="n">
-        <v>6.8</v>
+        <v>8.02</v>
       </c>
       <c r="I59" t="n">
-        <v>40.46</v>
+        <v>39.57</v>
       </c>
       <c r="J59" t="n">
-        <v>18.16</v>
+        <v>17.88</v>
       </c>
       <c r="K59" t="n">
-        <v>4.82</v>
+        <v>5.88</v>
       </c>
       <c r="L59" t="n">
-        <v>33.9</v>
+        <v>32.73</v>
       </c>
       <c r="M59" t="n">
-        <v>13.89</v>
+        <v>13.39</v>
       </c>
       <c r="N59" t="n">
-        <v>2.84</v>
+        <v>3.74</v>
       </c>
       <c r="O59" t="n">
-        <v>27.35</v>
+        <v>25.9</v>
       </c>
       <c r="P59" t="n">
-        <v>30.06</v>
+        <v>17.94</v>
       </c>
       <c r="Q59" t="n">
-        <v>-7.63</v>
+        <v>4.43</v>
       </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
@@ -3934,58 +3934,58 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Brevyn Spann-Ford</t>
+          <t>Adam Trautman</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>89.812</v>
+        <v>81.97499999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>0.736</v>
+        <v>0.796</v>
       </c>
       <c r="F60" t="n">
-        <v>8.977</v>
+        <v>8.772</v>
       </c>
       <c r="G60" t="n">
-        <v>22.37</v>
+        <v>21.74</v>
       </c>
       <c r="H60" t="n">
-        <v>8.02</v>
+        <v>7.08</v>
       </c>
       <c r="I60" t="n">
-        <v>39.57</v>
+        <v>39.18</v>
       </c>
       <c r="J60" t="n">
-        <v>17.88</v>
+        <v>17.36</v>
       </c>
       <c r="K60" t="n">
-        <v>5.88</v>
+        <v>5.02</v>
       </c>
       <c r="L60" t="n">
-        <v>32.73</v>
+        <v>32.47</v>
       </c>
       <c r="M60" t="n">
-        <v>13.39</v>
+        <v>12.97</v>
       </c>
       <c r="N60" t="n">
-        <v>3.74</v>
+        <v>2.96</v>
       </c>
       <c r="O60" t="n">
-        <v>25.9</v>
+        <v>25.76</v>
       </c>
       <c r="P60" t="n">
-        <v>17.94</v>
+        <v>21.53</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.43</v>
+        <v>0.21</v>
       </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -3993,58 +3993,58 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Adam Trautman</t>
+          <t>Sam Roush</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>81.97499999999999</v>
+        <v>85.059</v>
       </c>
       <c r="E61" t="n">
-        <v>0.796</v>
+        <v>0.781</v>
       </c>
       <c r="F61" t="n">
-        <v>8.772</v>
+        <v>7.446</v>
       </c>
       <c r="G61" t="n">
-        <v>21.74</v>
+        <v>20.64</v>
       </c>
       <c r="H61" t="n">
-        <v>7.08</v>
+        <v>6.44</v>
       </c>
       <c r="I61" t="n">
-        <v>39.18</v>
+        <v>37.62</v>
       </c>
       <c r="J61" t="n">
-        <v>17.36</v>
+        <v>16.92</v>
       </c>
       <c r="K61" t="n">
-        <v>5.02</v>
+        <v>4.85</v>
       </c>
       <c r="L61" t="n">
-        <v>32.47</v>
+        <v>31.76</v>
       </c>
       <c r="M61" t="n">
-        <v>12.97</v>
+        <v>13.19</v>
       </c>
       <c r="N61" t="n">
-        <v>2.96</v>
+        <v>3.26</v>
       </c>
       <c r="O61" t="n">
-        <v>25.76</v>
+        <v>25.9</v>
       </c>
       <c r="P61" t="n">
-        <v>21.53</v>
+        <v>21.65</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.21</v>
+        <v>-1.01</v>
       </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
@@ -4052,58 +4052,58 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sam Roush</t>
+          <t>Payne Durham</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>85.059</v>
+        <v>77.869</v>
       </c>
       <c r="E62" t="n">
-        <v>0.781</v>
+        <v>0.797</v>
       </c>
       <c r="F62" t="n">
-        <v>7.446</v>
+        <v>7.416</v>
       </c>
       <c r="G62" t="n">
-        <v>20.64</v>
+        <v>19.98</v>
       </c>
       <c r="H62" t="n">
-        <v>6.44</v>
+        <v>5.7</v>
       </c>
       <c r="I62" t="n">
-        <v>37.62</v>
+        <v>37.02</v>
       </c>
       <c r="J62" t="n">
-        <v>16.92</v>
+        <v>16.28</v>
       </c>
       <c r="K62" t="n">
-        <v>4.85</v>
+        <v>4.12</v>
       </c>
       <c r="L62" t="n">
-        <v>31.76</v>
+        <v>31.18</v>
       </c>
       <c r="M62" t="n">
-        <v>13.19</v>
+        <v>12.57</v>
       </c>
       <c r="N62" t="n">
-        <v>3.26</v>
+        <v>2.55</v>
       </c>
       <c r="O62" t="n">
-        <v>25.9</v>
+        <v>25.34</v>
       </c>
       <c r="P62" t="n">
-        <v>21.65</v>
+        <v>10.18</v>
       </c>
       <c r="Q62" t="n">
-        <v>-1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
@@ -4111,111 +4111,107 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Payne Durham</t>
+          <t>Blake Whiteheart</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>77.869</v>
+        <v>77.614</v>
       </c>
       <c r="E63" t="n">
-        <v>0.797</v>
+        <v>0.71</v>
       </c>
       <c r="F63" t="n">
-        <v>7.416</v>
+        <v>7.924</v>
       </c>
       <c r="G63" t="n">
-        <v>19.98</v>
+        <v>19.94</v>
       </c>
       <c r="H63" t="n">
-        <v>5.7</v>
+        <v>6.03</v>
       </c>
       <c r="I63" t="n">
-        <v>37.02</v>
+        <v>36.68</v>
       </c>
       <c r="J63" t="n">
-        <v>16.28</v>
+        <v>15.98</v>
       </c>
       <c r="K63" t="n">
-        <v>4.12</v>
+        <v>4.28</v>
       </c>
       <c r="L63" t="n">
-        <v>31.18</v>
+        <v>30.51</v>
       </c>
       <c r="M63" t="n">
-        <v>12.57</v>
+        <v>12.02</v>
       </c>
       <c r="N63" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="O63" t="n">
-        <v>25.34</v>
-      </c>
-      <c r="P63" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>24.34</v>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Blake Whiteheart</t>
+          <t>Eric Saubert</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>77.614</v>
+        <v>73.137</v>
       </c>
       <c r="E64" t="n">
-        <v>0.71</v>
+        <v>0.759</v>
       </c>
       <c r="F64" t="n">
-        <v>7.924</v>
+        <v>7.256</v>
       </c>
       <c r="G64" t="n">
-        <v>19.94</v>
+        <v>19.12</v>
       </c>
       <c r="H64" t="n">
-        <v>6.03</v>
+        <v>5.12</v>
       </c>
       <c r="I64" t="n">
-        <v>36.68</v>
+        <v>35.91</v>
       </c>
       <c r="J64" t="n">
-        <v>15.98</v>
+        <v>15.49</v>
       </c>
       <c r="K64" t="n">
-        <v>4.28</v>
+        <v>3.6</v>
       </c>
       <c r="L64" t="n">
-        <v>30.51</v>
+        <v>30.18</v>
       </c>
       <c r="M64" t="n">
-        <v>12.02</v>
+        <v>11.87</v>
       </c>
       <c r="N64" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="O64" t="n">
-        <v>24.34</v>
+        <v>24.44</v>
       </c>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
@@ -4225,113 +4221,117 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Eric Saubert</t>
+          <t>Johnny Mundt</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>73.137</v>
+        <v>68.673</v>
       </c>
       <c r="E65" t="n">
-        <v>0.759</v>
+        <v>0.793</v>
       </c>
       <c r="F65" t="n">
-        <v>7.256</v>
+        <v>7.227</v>
       </c>
       <c r="G65" t="n">
-        <v>19.12</v>
+        <v>18.85</v>
       </c>
       <c r="H65" t="n">
-        <v>5.12</v>
+        <v>4.65</v>
       </c>
       <c r="I65" t="n">
-        <v>35.91</v>
+        <v>35.79</v>
       </c>
       <c r="J65" t="n">
-        <v>15.49</v>
+        <v>15.24</v>
       </c>
       <c r="K65" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="L65" t="n">
-        <v>30.18</v>
+        <v>30.07</v>
       </c>
       <c r="M65" t="n">
-        <v>11.87</v>
+        <v>11.62</v>
       </c>
       <c r="N65" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="O65" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
+        <v>24.35</v>
+      </c>
+      <c r="P65" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>7.2</v>
+      </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Johnny Mundt</t>
+          <t>Charlie Woerner</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>68.673</v>
+        <v>72.584</v>
       </c>
       <c r="E66" t="n">
-        <v>0.793</v>
+        <v>0.663</v>
       </c>
       <c r="F66" t="n">
-        <v>7.227</v>
+        <v>7.308</v>
       </c>
       <c r="G66" t="n">
-        <v>18.85</v>
+        <v>18.54</v>
       </c>
       <c r="H66" t="n">
-        <v>4.65</v>
+        <v>5.1</v>
       </c>
       <c r="I66" t="n">
-        <v>35.79</v>
+        <v>34.9</v>
       </c>
       <c r="J66" t="n">
-        <v>15.24</v>
+        <v>14.89</v>
       </c>
       <c r="K66" t="n">
-        <v>3.14</v>
+        <v>3.56</v>
       </c>
       <c r="L66" t="n">
-        <v>30.07</v>
+        <v>29.13</v>
       </c>
       <c r="M66" t="n">
-        <v>11.62</v>
+        <v>11.24</v>
       </c>
       <c r="N66" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="O66" t="n">
-        <v>24.35</v>
+        <v>23.36</v>
       </c>
       <c r="P66" t="n">
-        <v>11.65</v>
+        <v>11.94</v>
       </c>
       <c r="Q66" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
@@ -4339,58 +4339,58 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Charlie Woerner</t>
+          <t>Luke Farrell</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>72.584</v>
+        <v>66.25700000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>0.663</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>7.308</v>
+        <v>7.046</v>
       </c>
       <c r="G67" t="n">
         <v>18.54</v>
       </c>
       <c r="H67" t="n">
-        <v>5.1</v>
+        <v>4.28</v>
       </c>
       <c r="I67" t="n">
-        <v>34.9</v>
+        <v>35.46</v>
       </c>
       <c r="J67" t="n">
-        <v>14.89</v>
+        <v>15.01</v>
       </c>
       <c r="K67" t="n">
-        <v>3.56</v>
+        <v>2.84</v>
       </c>
       <c r="L67" t="n">
-        <v>29.13</v>
+        <v>29.86</v>
       </c>
       <c r="M67" t="n">
-        <v>11.24</v>
+        <v>11.49</v>
       </c>
       <c r="N67" t="n">
-        <v>2.02</v>
+        <v>1.39</v>
       </c>
       <c r="O67" t="n">
-        <v>23.36</v>
+        <v>24.26</v>
       </c>
       <c r="P67" t="n">
-        <v>11.94</v>
+        <v>12.24</v>
       </c>
       <c r="Q67" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
@@ -4398,87 +4398,83 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Luke Farrell</t>
+          <t>Chris Manhertz</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>66.25700000000001</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.8110000000000001</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>7.046</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>18.54</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>35.46</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>15.01</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>29.86</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>11.49</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>24.26</v>
-      </c>
-      <c r="P68" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>6.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Chris Manhertz</t>
+          <t>Mo Alie-Cox</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>68.867</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.502</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>4.814</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>14.71</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -4487,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -4496,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -4504,36 +4500,40 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>-13.53</v>
+      </c>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mo Alie-Cox</t>
+          <t>Oronde Gadsden II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>51.281</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.573</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>5.773</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>14.34</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -4542,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>11.45</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>8.57</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
@@ -4560,10 +4560,10 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>13.53</v>
+        <v>63.28</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.8100000000000001</v>
+        <v>-63.28</v>
       </c>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
@@ -6399,83 +6399,87 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Hayden Rucci</t>
+          <t>Davis Allen</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>53.265</v>
+        <v>8.347</v>
       </c>
       <c r="E103" t="n">
-        <v>0.404</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F103" t="n">
-        <v>4.558</v>
+        <v>0.982</v>
       </c>
       <c r="G103" t="n">
-        <v>12.31</v>
+        <v>2.34</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="J103" t="n">
-        <v>10.03</v>
+        <v>1.85</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M103" t="n">
-        <v>7.75</v>
+        <v>1.36</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
+        <v>3.26</v>
+      </c>
+      <c r="P103" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>-14.66</v>
+      </c>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Thomas Fidone II</t>
+          <t>Andrew Ogletree</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>63.134</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>0.502</v>
+        <v>0</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>9.32</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -6484,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>9.32</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -6493,7 +6497,7 @@
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>9.32</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
         <v>0</v>
@@ -6502,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>6</v>
+        <v>11.65</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.32</v>
+        <v>-11.65</v>
       </c>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
@@ -6513,28 +6517,28 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Andrew Ogletree</t>
+          <t>Hayden Rucci</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>59.281</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>0.469</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>8.74</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -6543,7 +6547,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>8.74</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -6552,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>8.74</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
         <v>0</v>
@@ -6560,70 +6564,66 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="P105" t="n">
-        <v>11.65</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>-2.91</v>
-      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Davis Allen</t>
+          <t>Thomas Fidone II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>8.347</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0.982</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Q106" t="n">
-        <v>-14.66</v>
+        <v>-6</v>
       </c>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr"/>
@@ -8807,58 +8807,58 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Will Mallory</t>
+          <t>Tyler Higbee</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>143.257</v>
+        <v>29.288</v>
       </c>
       <c r="E37" t="n">
-        <v>0.866</v>
+        <v>0.228</v>
       </c>
       <c r="F37" t="n">
-        <v>11.671</v>
+        <v>3.128</v>
       </c>
       <c r="G37" t="n">
-        <v>31.19</v>
+        <v>7.43</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>13.08</v>
       </c>
       <c r="J37" t="n">
-        <v>25.36</v>
+        <v>5.86</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>10.85</v>
       </c>
       <c r="M37" t="n">
-        <v>19.52</v>
+        <v>4.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="P37" t="n">
-        <v>6.24</v>
+        <v>33.18</v>
       </c>
       <c r="Q37" t="n">
-        <v>24.95</v>
+        <v>-25.75</v>
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
@@ -8866,58 +8866,58 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tyler Higbee</t>
+          <t>Will Mallory</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>29.288</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.228</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>3.128</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>7.43</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>13.08</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>10.85</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>8.630000000000001</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>33.18</v>
+        <v>6.24</v>
       </c>
       <c r="Q38" t="n">
-        <v>-25.75</v>
+        <v>-6.24</v>
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -9913,58 +9913,58 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Oronde Gadsden II</t>
+          <t>Will Kacmarek</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>112.065</v>
+        <v>98.136</v>
       </c>
       <c r="E17" t="n">
-        <v>0.738</v>
+        <v>0.845</v>
       </c>
       <c r="F17" t="n">
-        <v>9.135</v>
+        <v>9.493</v>
       </c>
       <c r="G17" t="n">
-        <v>24.77</v>
+        <v>24.38</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>8.49</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>43.34</v>
       </c>
       <c r="J17" t="n">
-        <v>20.2</v>
+        <v>19.63</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>36.07</v>
       </c>
       <c r="M17" t="n">
-        <v>15.64</v>
+        <v>14.88</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>28.79</v>
       </c>
       <c r="P17" t="n">
-        <v>63.28</v>
+        <v>19.54</v>
       </c>
       <c r="Q17" t="n">
-        <v>-38.51</v>
+        <v>4.84</v>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
@@ -9972,58 +9972,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Will Kacmarek</t>
+          <t>Nate Boerkircher</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>98.136</v>
+        <v>96.67700000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.845</v>
+        <v>0.952</v>
       </c>
       <c r="F18" t="n">
-        <v>9.493</v>
+        <v>8.895</v>
       </c>
       <c r="G18" t="n">
-        <v>24.38</v>
+        <v>24.27</v>
       </c>
       <c r="H18" t="n">
-        <v>8.49</v>
+        <v>7.9</v>
       </c>
       <c r="I18" t="n">
-        <v>43.34</v>
+        <v>43.62</v>
       </c>
       <c r="J18" t="n">
-        <v>19.63</v>
+        <v>19.83</v>
       </c>
       <c r="K18" t="n">
-        <v>6.27</v>
+        <v>5.9</v>
       </c>
       <c r="L18" t="n">
-        <v>36.07</v>
+        <v>36.72</v>
       </c>
       <c r="M18" t="n">
-        <v>14.88</v>
+        <v>15.38</v>
       </c>
       <c r="N18" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="O18" t="n">
-        <v>28.79</v>
+        <v>29.82</v>
       </c>
       <c r="P18" t="n">
-        <v>19.54</v>
+        <v>28.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>-4.14</v>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -10031,58 +10031,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nate Boerkircher</t>
+          <t>Jonnu Smith</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>96.67700000000001</v>
+        <v>84.90900000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.952</v>
+        <v>0.978</v>
       </c>
       <c r="F19" t="n">
-        <v>8.895</v>
+        <v>9.456</v>
       </c>
       <c r="G19" t="n">
-        <v>24.27</v>
+        <v>23.82</v>
       </c>
       <c r="H19" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
       <c r="I19" t="n">
-        <v>43.62</v>
+        <v>42.21</v>
       </c>
       <c r="J19" t="n">
-        <v>19.83</v>
+        <v>19.09</v>
       </c>
       <c r="K19" t="n">
-        <v>5.9</v>
+        <v>5.58</v>
       </c>
       <c r="L19" t="n">
-        <v>36.72</v>
+        <v>35.08</v>
       </c>
       <c r="M19" t="n">
-        <v>15.38</v>
+        <v>14.36</v>
       </c>
       <c r="N19" t="n">
-        <v>3.91</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>29.82</v>
+        <v>27.95</v>
       </c>
       <c r="P19" t="n">
-        <v>28.41</v>
+        <v>20.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.14</v>
+        <v>2.94</v>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -10090,58 +10090,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jonnu Smith</t>
+          <t>Brock Wright</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>84.90900000000001</v>
+        <v>76.95</v>
       </c>
       <c r="E20" t="n">
-        <v>0.978</v>
+        <v>0.928</v>
       </c>
       <c r="F20" t="n">
-        <v>9.456</v>
+        <v>9.519</v>
       </c>
       <c r="G20" t="n">
-        <v>23.82</v>
+        <v>22.78</v>
       </c>
       <c r="H20" t="n">
-        <v>7.91</v>
+        <v>6.39</v>
       </c>
       <c r="I20" t="n">
-        <v>42.21</v>
+        <v>42.08</v>
       </c>
       <c r="J20" t="n">
-        <v>19.09</v>
+        <v>18.02</v>
       </c>
       <c r="K20" t="n">
-        <v>5.58</v>
+        <v>4.16</v>
       </c>
       <c r="L20" t="n">
-        <v>35.08</v>
+        <v>34.79</v>
       </c>
       <c r="M20" t="n">
-        <v>14.36</v>
+        <v>13.26</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>1.93</v>
       </c>
       <c r="O20" t="n">
-        <v>27.95</v>
+        <v>27.5</v>
       </c>
       <c r="P20" t="n">
-        <v>20.88</v>
+        <v>22.65</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.94</v>
+        <v>0.13</v>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -10149,58 +10149,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brock Wright</t>
+          <t>Foster Moreau</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>76.95</v>
+        <v>80.744</v>
       </c>
       <c r="E21" t="n">
-        <v>0.928</v>
+        <v>0.97</v>
       </c>
       <c r="F21" t="n">
-        <v>9.519</v>
+        <v>8.539</v>
       </c>
       <c r="G21" t="n">
-        <v>22.78</v>
+        <v>22.43</v>
       </c>
       <c r="H21" t="n">
-        <v>6.39</v>
+        <v>6.8</v>
       </c>
       <c r="I21" t="n">
-        <v>42.08</v>
+        <v>40.46</v>
       </c>
       <c r="J21" t="n">
-        <v>18.02</v>
+        <v>18.16</v>
       </c>
       <c r="K21" t="n">
-        <v>4.16</v>
+        <v>4.82</v>
       </c>
       <c r="L21" t="n">
-        <v>34.79</v>
+        <v>33.9</v>
       </c>
       <c r="M21" t="n">
-        <v>13.26</v>
+        <v>13.89</v>
       </c>
       <c r="N21" t="n">
-        <v>1.93</v>
+        <v>2.84</v>
       </c>
       <c r="O21" t="n">
-        <v>27.5</v>
+        <v>27.35</v>
       </c>
       <c r="P21" t="n">
-        <v>22.65</v>
+        <v>30.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.13</v>
+        <v>-7.63</v>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
@@ -10208,58 +10208,58 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Foster Moreau</t>
+          <t>Brevyn Spann-Ford</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>80.744</v>
+        <v>89.812</v>
       </c>
       <c r="E22" t="n">
-        <v>0.97</v>
+        <v>0.736</v>
       </c>
       <c r="F22" t="n">
-        <v>8.539</v>
+        <v>8.977</v>
       </c>
       <c r="G22" t="n">
-        <v>22.43</v>
+        <v>22.37</v>
       </c>
       <c r="H22" t="n">
-        <v>6.8</v>
+        <v>8.02</v>
       </c>
       <c r="I22" t="n">
-        <v>40.46</v>
+        <v>39.57</v>
       </c>
       <c r="J22" t="n">
-        <v>18.16</v>
+        <v>17.88</v>
       </c>
       <c r="K22" t="n">
-        <v>4.82</v>
+        <v>5.88</v>
       </c>
       <c r="L22" t="n">
-        <v>33.9</v>
+        <v>32.73</v>
       </c>
       <c r="M22" t="n">
-        <v>13.89</v>
+        <v>13.39</v>
       </c>
       <c r="N22" t="n">
-        <v>2.84</v>
+        <v>3.74</v>
       </c>
       <c r="O22" t="n">
-        <v>27.35</v>
+        <v>25.9</v>
       </c>
       <c r="P22" t="n">
-        <v>30.06</v>
+        <v>17.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>-7.63</v>
+        <v>4.43</v>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
@@ -10267,58 +10267,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brevyn Spann-Ford</t>
+          <t>Adam Trautman</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>89.812</v>
+        <v>81.97499999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>0.736</v>
+        <v>0.796</v>
       </c>
       <c r="F23" t="n">
-        <v>8.977</v>
+        <v>8.772</v>
       </c>
       <c r="G23" t="n">
-        <v>22.37</v>
+        <v>21.74</v>
       </c>
       <c r="H23" t="n">
-        <v>8.02</v>
+        <v>7.08</v>
       </c>
       <c r="I23" t="n">
-        <v>39.57</v>
+        <v>39.18</v>
       </c>
       <c r="J23" t="n">
-        <v>17.88</v>
+        <v>17.36</v>
       </c>
       <c r="K23" t="n">
-        <v>5.88</v>
+        <v>5.02</v>
       </c>
       <c r="L23" t="n">
-        <v>32.73</v>
+        <v>32.47</v>
       </c>
       <c r="M23" t="n">
-        <v>13.39</v>
+        <v>12.97</v>
       </c>
       <c r="N23" t="n">
-        <v>3.74</v>
+        <v>2.96</v>
       </c>
       <c r="O23" t="n">
-        <v>25.9</v>
+        <v>25.76</v>
       </c>
       <c r="P23" t="n">
-        <v>17.94</v>
+        <v>21.53</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.43</v>
+        <v>0.21</v>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -10326,58 +10326,58 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Adam Trautman</t>
+          <t>Sam Roush</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>81.97499999999999</v>
+        <v>85.059</v>
       </c>
       <c r="E24" t="n">
-        <v>0.796</v>
+        <v>0.781</v>
       </c>
       <c r="F24" t="n">
-        <v>8.772</v>
+        <v>7.446</v>
       </c>
       <c r="G24" t="n">
-        <v>21.74</v>
+        <v>20.64</v>
       </c>
       <c r="H24" t="n">
-        <v>7.08</v>
+        <v>6.44</v>
       </c>
       <c r="I24" t="n">
-        <v>39.18</v>
+        <v>37.62</v>
       </c>
       <c r="J24" t="n">
-        <v>17.36</v>
+        <v>16.92</v>
       </c>
       <c r="K24" t="n">
-        <v>5.02</v>
+        <v>4.85</v>
       </c>
       <c r="L24" t="n">
-        <v>32.47</v>
+        <v>31.76</v>
       </c>
       <c r="M24" t="n">
-        <v>12.97</v>
+        <v>13.19</v>
       </c>
       <c r="N24" t="n">
-        <v>2.96</v>
+        <v>3.26</v>
       </c>
       <c r="O24" t="n">
-        <v>25.76</v>
+        <v>25.9</v>
       </c>
       <c r="P24" t="n">
-        <v>21.53</v>
+        <v>21.65</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.21</v>
+        <v>-1.01</v>
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
@@ -10385,58 +10385,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sam Roush</t>
+          <t>Payne Durham</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>85.059</v>
+        <v>77.869</v>
       </c>
       <c r="E25" t="n">
-        <v>0.781</v>
+        <v>0.797</v>
       </c>
       <c r="F25" t="n">
-        <v>7.446</v>
+        <v>7.416</v>
       </c>
       <c r="G25" t="n">
-        <v>20.64</v>
+        <v>19.98</v>
       </c>
       <c r="H25" t="n">
-        <v>6.44</v>
+        <v>5.7</v>
       </c>
       <c r="I25" t="n">
-        <v>37.62</v>
+        <v>37.02</v>
       </c>
       <c r="J25" t="n">
-        <v>16.92</v>
+        <v>16.28</v>
       </c>
       <c r="K25" t="n">
-        <v>4.85</v>
+        <v>4.12</v>
       </c>
       <c r="L25" t="n">
-        <v>31.76</v>
+        <v>31.18</v>
       </c>
       <c r="M25" t="n">
-        <v>13.19</v>
+        <v>12.57</v>
       </c>
       <c r="N25" t="n">
-        <v>3.26</v>
+        <v>2.55</v>
       </c>
       <c r="O25" t="n">
-        <v>25.9</v>
+        <v>25.34</v>
       </c>
       <c r="P25" t="n">
-        <v>21.65</v>
+        <v>10.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
@@ -10444,111 +10444,107 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Payne Durham</t>
+          <t>Blake Whiteheart</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>77.869</v>
+        <v>77.614</v>
       </c>
       <c r="E26" t="n">
-        <v>0.797</v>
+        <v>0.71</v>
       </c>
       <c r="F26" t="n">
-        <v>7.416</v>
+        <v>7.924</v>
       </c>
       <c r="G26" t="n">
-        <v>19.98</v>
+        <v>19.94</v>
       </c>
       <c r="H26" t="n">
-        <v>5.7</v>
+        <v>6.03</v>
       </c>
       <c r="I26" t="n">
-        <v>37.02</v>
+        <v>36.68</v>
       </c>
       <c r="J26" t="n">
-        <v>16.28</v>
+        <v>15.98</v>
       </c>
       <c r="K26" t="n">
-        <v>4.12</v>
+        <v>4.28</v>
       </c>
       <c r="L26" t="n">
-        <v>31.18</v>
+        <v>30.51</v>
       </c>
       <c r="M26" t="n">
-        <v>12.57</v>
+        <v>12.02</v>
       </c>
       <c r="N26" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="O26" t="n">
-        <v>25.34</v>
-      </c>
-      <c r="P26" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>24.34</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Blake Whiteheart</t>
+          <t>Eric Saubert</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>77.614</v>
+        <v>73.137</v>
       </c>
       <c r="E27" t="n">
-        <v>0.71</v>
+        <v>0.759</v>
       </c>
       <c r="F27" t="n">
-        <v>7.924</v>
+        <v>7.256</v>
       </c>
       <c r="G27" t="n">
-        <v>19.94</v>
+        <v>19.12</v>
       </c>
       <c r="H27" t="n">
-        <v>6.03</v>
+        <v>5.12</v>
       </c>
       <c r="I27" t="n">
-        <v>36.68</v>
+        <v>35.91</v>
       </c>
       <c r="J27" t="n">
-        <v>15.98</v>
+        <v>15.49</v>
       </c>
       <c r="K27" t="n">
-        <v>4.28</v>
+        <v>3.6</v>
       </c>
       <c r="L27" t="n">
-        <v>30.51</v>
+        <v>30.18</v>
       </c>
       <c r="M27" t="n">
-        <v>12.02</v>
+        <v>11.87</v>
       </c>
       <c r="N27" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="O27" t="n">
-        <v>24.34</v>
+        <v>24.44</v>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -10558,113 +10554,117 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Eric Saubert</t>
+          <t>Johnny Mundt</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>73.137</v>
+        <v>68.673</v>
       </c>
       <c r="E28" t="n">
-        <v>0.759</v>
+        <v>0.793</v>
       </c>
       <c r="F28" t="n">
-        <v>7.256</v>
+        <v>7.227</v>
       </c>
       <c r="G28" t="n">
-        <v>19.12</v>
+        <v>18.85</v>
       </c>
       <c r="H28" t="n">
-        <v>5.12</v>
+        <v>4.65</v>
       </c>
       <c r="I28" t="n">
-        <v>35.91</v>
+        <v>35.79</v>
       </c>
       <c r="J28" t="n">
-        <v>15.49</v>
+        <v>15.24</v>
       </c>
       <c r="K28" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="L28" t="n">
-        <v>30.18</v>
+        <v>30.07</v>
       </c>
       <c r="M28" t="n">
-        <v>11.87</v>
+        <v>11.62</v>
       </c>
       <c r="N28" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="O28" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+        <v>24.35</v>
+      </c>
+      <c r="P28" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>7.2</v>
+      </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Johnny Mundt</t>
+          <t>Charlie Woerner</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>68.673</v>
+        <v>72.584</v>
       </c>
       <c r="E29" t="n">
-        <v>0.793</v>
+        <v>0.663</v>
       </c>
       <c r="F29" t="n">
-        <v>7.227</v>
+        <v>7.308</v>
       </c>
       <c r="G29" t="n">
-        <v>18.85</v>
+        <v>18.54</v>
       </c>
       <c r="H29" t="n">
-        <v>4.65</v>
+        <v>5.1</v>
       </c>
       <c r="I29" t="n">
-        <v>35.79</v>
+        <v>34.9</v>
       </c>
       <c r="J29" t="n">
-        <v>15.24</v>
+        <v>14.89</v>
       </c>
       <c r="K29" t="n">
-        <v>3.14</v>
+        <v>3.56</v>
       </c>
       <c r="L29" t="n">
-        <v>30.07</v>
+        <v>29.13</v>
       </c>
       <c r="M29" t="n">
-        <v>11.62</v>
+        <v>11.24</v>
       </c>
       <c r="N29" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="O29" t="n">
-        <v>24.35</v>
+        <v>23.36</v>
       </c>
       <c r="P29" t="n">
-        <v>11.65</v>
+        <v>11.94</v>
       </c>
       <c r="Q29" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
@@ -10672,58 +10672,58 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Charlie Woerner</t>
+          <t>Luke Farrell</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>72.584</v>
+        <v>66.25700000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.663</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>7.308</v>
+        <v>7.046</v>
       </c>
       <c r="G30" t="n">
         <v>18.54</v>
       </c>
       <c r="H30" t="n">
-        <v>5.1</v>
+        <v>4.28</v>
       </c>
       <c r="I30" t="n">
-        <v>34.9</v>
+        <v>35.46</v>
       </c>
       <c r="J30" t="n">
-        <v>14.89</v>
+        <v>15.01</v>
       </c>
       <c r="K30" t="n">
-        <v>3.56</v>
+        <v>2.84</v>
       </c>
       <c r="L30" t="n">
-        <v>29.13</v>
+        <v>29.86</v>
       </c>
       <c r="M30" t="n">
-        <v>11.24</v>
+        <v>11.49</v>
       </c>
       <c r="N30" t="n">
-        <v>2.02</v>
+        <v>1.39</v>
       </c>
       <c r="O30" t="n">
-        <v>23.36</v>
+        <v>24.26</v>
       </c>
       <c r="P30" t="n">
-        <v>11.94</v>
+        <v>12.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
@@ -10731,87 +10731,83 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Luke Farrell</t>
+          <t>Chris Manhertz</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>66.25700000000001</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8110000000000001</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>7.046</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>18.54</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>35.46</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>15.01</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>29.86</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>11.49</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>24.26</v>
-      </c>
-      <c r="P31" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>6.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Chris Manhertz</t>
+          <t>Mo Alie-Cox</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>68.867</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.502</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>4.814</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>14.71</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -10820,7 +10816,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -10829,7 +10825,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -10837,36 +10833,40 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-13.53</v>
+      </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mo Alie-Cox</t>
+          <t>Oronde Gadsden II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>51.281</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.573</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>5.773</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>14.34</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -10875,7 +10875,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>11.45</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -10884,7 +10884,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>8.57</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>13.53</v>
+        <v>63.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.8100000000000001</v>
+        <v>-63.28</v>
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -12843,83 +12843,87 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Hayden Rucci</t>
+          <t>Davis Allen</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>53.265</v>
+        <v>8.347</v>
       </c>
       <c r="E34" t="n">
-        <v>0.404</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>4.558</v>
+        <v>0.982</v>
       </c>
       <c r="G34" t="n">
-        <v>12.31</v>
+        <v>2.34</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="J34" t="n">
-        <v>10.03</v>
+        <v>1.85</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M34" t="n">
-        <v>7.75</v>
+        <v>1.36</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+        <v>3.26</v>
+      </c>
+      <c r="P34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-14.66</v>
+      </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Thomas Fidone II</t>
+          <t>Andrew Ogletree</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>63.134</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.502</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>9.32</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -12928,7 +12932,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>9.32</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -12937,7 +12941,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>9.32</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -12946,10 +12950,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>6</v>
+        <v>11.65</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.32</v>
+        <v>-11.65</v>
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -12957,28 +12961,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Andrew Ogletree</t>
+          <t>Hayden Rucci</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>59.281</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.469</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>8.74</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -12987,7 +12991,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>8.74</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -12996,7 +13000,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>8.74</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -13004,70 +13008,66 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="P36" t="n">
-        <v>11.65</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>-2.91</v>
-      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Davis Allen</t>
+          <t>Thomas Fidone II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>8.347</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.982</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Q37" t="n">
-        <v>-14.66</v>
+        <v>-6</v>
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>

--- a/projections/te_2026_combined.xlsx
+++ b/projections/te_2026_combined.xlsx
@@ -780,28 +780,28 @@
         <v>118.09</v>
       </c>
       <c r="H6" t="n">
-        <v>64.11</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>173.06</v>
+        <v>159.41</v>
       </c>
       <c r="J6" t="n">
         <v>96.56</v>
       </c>
       <c r="K6" t="n">
-        <v>49.59</v>
+        <v>60.87</v>
       </c>
       <c r="L6" t="n">
-        <v>144.52</v>
+        <v>132.25</v>
       </c>
       <c r="M6" t="n">
         <v>75.03</v>
       </c>
       <c r="N6" t="n">
-        <v>35.07</v>
+        <v>44.98</v>
       </c>
       <c r="O6" t="n">
-        <v>115.99</v>
+        <v>105.08</v>
       </c>
       <c r="P6" t="n">
         <v>119.45</v>
@@ -839,28 +839,28 @@
         <v>113.9</v>
       </c>
       <c r="H7" t="n">
-        <v>63.36</v>
+        <v>75.89</v>
       </c>
       <c r="I7" t="n">
-        <v>167.69</v>
+        <v>151.9</v>
       </c>
       <c r="J7" t="n">
         <v>86.98</v>
       </c>
       <c r="K7" t="n">
-        <v>44.28</v>
+        <v>54.99</v>
       </c>
       <c r="L7" t="n">
-        <v>132.94</v>
+        <v>118.96</v>
       </c>
       <c r="M7" t="n">
         <v>60.07</v>
       </c>
       <c r="N7" t="n">
-        <v>25.2</v>
+        <v>34.09</v>
       </c>
       <c r="O7" t="n">
-        <v>98.19</v>
+        <v>86.03</v>
       </c>
       <c r="P7" t="n">
         <v>132.59</v>
@@ -1075,28 +1075,28 @@
         <v>105.41</v>
       </c>
       <c r="H11" t="n">
-        <v>67.87</v>
+        <v>54.39</v>
       </c>
       <c r="I11" t="n">
-        <v>142.95</v>
+        <v>158.59</v>
       </c>
       <c r="J11" t="n">
         <v>85.42</v>
       </c>
       <c r="K11" t="n">
-        <v>53.05</v>
+        <v>41.14</v>
       </c>
       <c r="L11" t="n">
-        <v>117.78</v>
+        <v>131.84</v>
       </c>
       <c r="M11" t="n">
         <v>65.42</v>
       </c>
       <c r="N11" t="n">
-        <v>38.23</v>
+        <v>27.9</v>
       </c>
       <c r="O11" t="n">
-        <v>92.59999999999999</v>
+        <v>105.09</v>
       </c>
       <c r="P11" t="n">
         <v>141.18</v>
@@ -1429,28 +1429,28 @@
         <v>94.63</v>
       </c>
       <c r="H17" t="n">
-        <v>48.92</v>
+        <v>58.04</v>
       </c>
       <c r="I17" t="n">
-        <v>144.49</v>
+        <v>131.86</v>
       </c>
       <c r="J17" t="n">
         <v>75.31999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>36.25</v>
+        <v>44.07</v>
       </c>
       <c r="L17" t="n">
-        <v>118.56</v>
+        <v>107.22</v>
       </c>
       <c r="M17" t="n">
         <v>56.02</v>
       </c>
       <c r="N17" t="n">
-        <v>23.58</v>
+        <v>30.1</v>
       </c>
       <c r="O17" t="n">
-        <v>92.62</v>
+        <v>82.58</v>
       </c>
       <c r="P17" t="n">
         <v>71.31</v>
@@ -3258,28 +3258,28 @@
         <v>27.55</v>
       </c>
       <c r="H48" t="n">
-        <v>6.54</v>
+        <v>10.95</v>
       </c>
       <c r="I48" t="n">
-        <v>53.61</v>
+        <v>47.11</v>
       </c>
       <c r="J48" t="n">
         <v>22.44</v>
       </c>
       <c r="K48" t="n">
-        <v>4.69</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>45.22</v>
+        <v>39.36</v>
       </c>
       <c r="M48" t="n">
         <v>17.32</v>
       </c>
       <c r="N48" t="n">
-        <v>2.83</v>
+        <v>5.97</v>
       </c>
       <c r="O48" t="n">
-        <v>36.84</v>
+        <v>31.62</v>
       </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
@@ -3545,28 +3545,28 @@
         <v>24.37</v>
       </c>
       <c r="H53" t="n">
-        <v>4.1</v>
+        <v>8.48</v>
       </c>
       <c r="I53" t="n">
-        <v>49.68</v>
+        <v>43.34</v>
       </c>
       <c r="J53" t="n">
         <v>19.62</v>
       </c>
       <c r="K53" t="n">
-        <v>2.5</v>
+        <v>6.26</v>
       </c>
       <c r="L53" t="n">
-        <v>41.79</v>
+        <v>36.07</v>
       </c>
       <c r="M53" t="n">
         <v>14.88</v>
       </c>
       <c r="N53" t="n">
-        <v>0.9</v>
+        <v>4.04</v>
       </c>
       <c r="O53" t="n">
-        <v>33.9</v>
+        <v>28.79</v>
       </c>
       <c r="P53" t="n">
         <v>19.54</v>
@@ -5963,28 +5963,28 @@
         <v>19.15</v>
       </c>
       <c r="H95" t="n">
-        <v>2.76</v>
+        <v>6.59</v>
       </c>
       <c r="I95" t="n">
-        <v>40.5</v>
+        <v>34.41</v>
       </c>
       <c r="J95" t="n">
         <v>15.21</v>
       </c>
       <c r="K95" t="n">
-        <v>1.64</v>
+        <v>4.82</v>
       </c>
       <c r="L95" t="n">
-        <v>33.75</v>
+        <v>28.31</v>
       </c>
       <c r="M95" t="n">
         <v>11.28</v>
       </c>
       <c r="N95" t="n">
-        <v>0.53</v>
+        <v>3.05</v>
       </c>
       <c r="O95" t="n">
-        <v>26.99</v>
+        <v>22.2</v>
       </c>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
@@ -6707,28 +6707,28 @@
         <v>118.09</v>
       </c>
       <c r="H6" t="n">
-        <v>64.11</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>173.06</v>
+        <v>159.41</v>
       </c>
       <c r="J6" t="n">
         <v>96.56</v>
       </c>
       <c r="K6" t="n">
-        <v>49.59</v>
+        <v>60.87</v>
       </c>
       <c r="L6" t="n">
-        <v>144.52</v>
+        <v>132.25</v>
       </c>
       <c r="M6" t="n">
         <v>75.03</v>
       </c>
       <c r="N6" t="n">
-        <v>35.07</v>
+        <v>44.98</v>
       </c>
       <c r="O6" t="n">
-        <v>115.99</v>
+        <v>105.08</v>
       </c>
       <c r="P6" t="n">
         <v>119.45</v>
@@ -6766,28 +6766,28 @@
         <v>113.9</v>
       </c>
       <c r="H7" t="n">
-        <v>63.36</v>
+        <v>75.89</v>
       </c>
       <c r="I7" t="n">
-        <v>167.69</v>
+        <v>151.9</v>
       </c>
       <c r="J7" t="n">
         <v>86.98</v>
       </c>
       <c r="K7" t="n">
-        <v>44.28</v>
+        <v>54.99</v>
       </c>
       <c r="L7" t="n">
-        <v>132.94</v>
+        <v>118.96</v>
       </c>
       <c r="M7" t="n">
         <v>60.07</v>
       </c>
       <c r="N7" t="n">
-        <v>25.2</v>
+        <v>34.09</v>
       </c>
       <c r="O7" t="n">
-        <v>98.19</v>
+        <v>86.03</v>
       </c>
       <c r="P7" t="n">
         <v>132.59</v>
@@ -7002,28 +7002,28 @@
         <v>105.41</v>
       </c>
       <c r="H11" t="n">
-        <v>67.87</v>
+        <v>54.39</v>
       </c>
       <c r="I11" t="n">
-        <v>142.95</v>
+        <v>158.59</v>
       </c>
       <c r="J11" t="n">
         <v>85.42</v>
       </c>
       <c r="K11" t="n">
-        <v>53.05</v>
+        <v>41.14</v>
       </c>
       <c r="L11" t="n">
-        <v>117.78</v>
+        <v>131.84</v>
       </c>
       <c r="M11" t="n">
         <v>65.42</v>
       </c>
       <c r="N11" t="n">
-        <v>38.23</v>
+        <v>27.9</v>
       </c>
       <c r="O11" t="n">
-        <v>92.59999999999999</v>
+        <v>105.09</v>
       </c>
       <c r="P11" t="n">
         <v>141.18</v>
@@ -7356,28 +7356,28 @@
         <v>94.63</v>
       </c>
       <c r="H17" t="n">
-        <v>48.92</v>
+        <v>58.04</v>
       </c>
       <c r="I17" t="n">
-        <v>144.49</v>
+        <v>131.86</v>
       </c>
       <c r="J17" t="n">
         <v>75.31999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>36.25</v>
+        <v>44.07</v>
       </c>
       <c r="L17" t="n">
-        <v>118.56</v>
+        <v>107.22</v>
       </c>
       <c r="M17" t="n">
         <v>56.02</v>
       </c>
       <c r="N17" t="n">
-        <v>23.58</v>
+        <v>30.1</v>
       </c>
       <c r="O17" t="n">
-        <v>92.62</v>
+        <v>82.58</v>
       </c>
       <c r="P17" t="n">
         <v>71.31</v>
@@ -9296,28 +9296,28 @@
         <v>27.55</v>
       </c>
       <c r="H12" t="n">
-        <v>6.54</v>
+        <v>10.95</v>
       </c>
       <c r="I12" t="n">
-        <v>53.61</v>
+        <v>47.11</v>
       </c>
       <c r="J12" t="n">
         <v>22.44</v>
       </c>
       <c r="K12" t="n">
-        <v>4.69</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>45.22</v>
+        <v>39.36</v>
       </c>
       <c r="M12" t="n">
         <v>17.32</v>
       </c>
       <c r="N12" t="n">
-        <v>2.83</v>
+        <v>5.97</v>
       </c>
       <c r="O12" t="n">
-        <v>36.84</v>
+        <v>31.62</v>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -9583,28 +9583,28 @@
         <v>24.37</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1</v>
+        <v>8.48</v>
       </c>
       <c r="I17" t="n">
-        <v>49.68</v>
+        <v>43.34</v>
       </c>
       <c r="J17" t="n">
         <v>19.62</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5</v>
+        <v>6.26</v>
       </c>
       <c r="L17" t="n">
-        <v>41.79</v>
+        <v>36.07</v>
       </c>
       <c r="M17" t="n">
         <v>14.88</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9</v>
+        <v>4.04</v>
       </c>
       <c r="O17" t="n">
-        <v>33.9</v>
+        <v>28.79</v>
       </c>
       <c r="P17" t="n">
         <v>19.54</v>
@@ -12112,28 +12112,28 @@
         <v>19.15</v>
       </c>
       <c r="H29" t="n">
-        <v>2.76</v>
+        <v>6.59</v>
       </c>
       <c r="I29" t="n">
-        <v>40.5</v>
+        <v>34.41</v>
       </c>
       <c r="J29" t="n">
         <v>15.21</v>
       </c>
       <c r="K29" t="n">
-        <v>1.64</v>
+        <v>4.82</v>
       </c>
       <c r="L29" t="n">
-        <v>33.75</v>
+        <v>28.31</v>
       </c>
       <c r="M29" t="n">
         <v>11.28</v>
       </c>
       <c r="N29" t="n">
-        <v>0.53</v>
+        <v>3.05</v>
       </c>
       <c r="O29" t="n">
-        <v>26.99</v>
+        <v>22.2</v>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
